--- a/Treinamento/RecusaPropostasAuto_06.05.2024.xlsx
+++ b/Treinamento/RecusaPropostasAuto_06.05.2024.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Bloqueios\Robô gera GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF6CB61B-5C8C-48C7-AC53-26EE6C860FB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02BC24BB-53FC-48CD-9B87-A1A3F83FF889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{2B38B9FE-A6BA-4F96-8BE8-CCEB7CBF2D90}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{2B38B9FE-A6BA-4F96-8BE8-CCEB7CBF2D90}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$2:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$A$314</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="3">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="3">
   <si>
     <t>Proposta</t>
   </si>
@@ -410,15 +410,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C5B2D2D-F842-483F-B782-CCB2AEB4A0EC}">
-  <dimension ref="A1:B315"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B314"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.54296875" customWidth="1"/>
-    <col min="2" max="2" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -426,7 +426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>123848933</v>
       </c>
@@ -434,7 +434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>123912048</v>
       </c>
@@ -442,7 +442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>123918964</v>
       </c>
@@ -450,7 +450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>123939765</v>
       </c>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>123951854</v>
       </c>
@@ -466,7 +466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>124110599</v>
       </c>
@@ -474,7 +474,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>124162274</v>
       </c>
@@ -482,7 +482,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>124170464</v>
       </c>
@@ -490,7 +490,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>124173175</v>
       </c>
@@ -498,7 +498,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>124206148</v>
       </c>
@@ -506,7 +506,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>124256909</v>
       </c>
@@ -514,7 +514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>124285986</v>
       </c>
@@ -522,7 +522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>124316790</v>
       </c>
@@ -530,7 +530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>124344836</v>
       </c>
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>124363279</v>
       </c>
@@ -546,7 +546,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>124427465</v>
       </c>
@@ -554,7 +554,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>124489607</v>
       </c>
@@ -562,7 +562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>124618185</v>
       </c>
@@ -570,7 +570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>124634192</v>
       </c>
@@ -578,7 +578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>124653754</v>
       </c>
@@ -586,7 +586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>124670595</v>
       </c>
@@ -594,7 +594,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>124686339</v>
       </c>
@@ -602,7 +602,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>124831020</v>
       </c>
@@ -610,7 +610,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>124893866</v>
       </c>
@@ -618,7 +618,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>124990740</v>
       </c>
@@ -626,7 +626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>125043215</v>
       </c>
@@ -634,7 +634,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>125121353</v>
       </c>
@@ -642,7 +642,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>125217938</v>
       </c>
@@ -650,7 +650,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>125255732</v>
       </c>
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>125265503</v>
       </c>
@@ -666,7 +666,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>125282610</v>
       </c>
@@ -674,7 +674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>125319916</v>
       </c>
@@ -682,7 +682,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>125328020</v>
       </c>
@@ -690,7 +690,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>125454336</v>
       </c>
@@ -698,7 +698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>125511004</v>
       </c>
@@ -706,7 +706,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>125560935</v>
       </c>
@@ -714,7 +714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>125702925</v>
       </c>
@@ -722,7 +722,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>125741439</v>
       </c>
@@ -730,7 +730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>125758082</v>
       </c>
@@ -738,7 +738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>125758802</v>
       </c>
@@ -746,7 +746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>125801674</v>
       </c>
@@ -754,7 +754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>125818658</v>
       </c>
@@ -762,7 +762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>125868394</v>
       </c>
@@ -770,7 +770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>125909673</v>
       </c>
@@ -778,7 +778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>125967352</v>
       </c>
@@ -786,7 +786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>125994900</v>
       </c>
@@ -794,7 +794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>126024813</v>
       </c>
@@ -802,2139 +802,2131 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>126072817</v>
+        <v>126085176</v>
       </c>
       <c r="B49" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>126085176</v>
+        <v>126089557</v>
       </c>
       <c r="B50" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>126089557</v>
+        <v>126095381</v>
       </c>
       <c r="B51" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>126095381</v>
+        <v>126096869</v>
       </c>
       <c r="B52" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>126096869</v>
+        <v>126113404</v>
       </c>
       <c r="B53" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>126113404</v>
+        <v>126167370</v>
       </c>
       <c r="B54" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>126167370</v>
+        <v>126195217</v>
       </c>
       <c r="B55" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>126195217</v>
+        <v>126195599</v>
       </c>
       <c r="B56" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>126195599</v>
+        <v>126243552</v>
       </c>
       <c r="B57" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>126243552</v>
+        <v>126297974</v>
       </c>
       <c r="B58" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>126297974</v>
+        <v>126569596</v>
       </c>
       <c r="B59" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>126569596</v>
+        <v>126595878</v>
       </c>
       <c r="B60" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>126595878</v>
+        <v>126739295</v>
       </c>
       <c r="B61" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>126739295</v>
+        <v>126981904</v>
       </c>
       <c r="B62" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>126981904</v>
+        <v>127101911</v>
       </c>
       <c r="B63" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>127101911</v>
+        <v>127161461</v>
       </c>
       <c r="B64" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>127161461</v>
+        <v>127367808</v>
       </c>
       <c r="B65" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>127367808</v>
+        <v>127376387</v>
       </c>
       <c r="B66" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>127376387</v>
+        <v>127498745</v>
       </c>
       <c r="B67" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>127498745</v>
+        <v>127498777</v>
       </c>
       <c r="B68" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69">
-        <v>127498777</v>
+        <v>127498786</v>
       </c>
       <c r="B69" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70">
-        <v>127498786</v>
+        <v>127498844</v>
       </c>
       <c r="B70" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>127498844</v>
+        <v>127498864</v>
       </c>
       <c r="B71" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>127498864</v>
+        <v>127498888</v>
       </c>
       <c r="B72" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>127498888</v>
+        <v>127498964</v>
       </c>
       <c r="B73" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74">
-        <v>127498964</v>
+        <v>127499154</v>
       </c>
       <c r="B74" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75">
-        <v>127499154</v>
+        <v>127499179</v>
       </c>
       <c r="B75" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76">
-        <v>127499179</v>
+        <v>127499215</v>
       </c>
       <c r="B76" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77">
-        <v>127499215</v>
+        <v>127499223</v>
       </c>
       <c r="B77" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78">
-        <v>127499223</v>
+        <v>127499307</v>
       </c>
       <c r="B78" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79">
-        <v>127499307</v>
+        <v>127499353</v>
       </c>
       <c r="B79" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80">
-        <v>127499353</v>
+        <v>127499482</v>
       </c>
       <c r="B80" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81">
-        <v>127499482</v>
+        <v>127499607</v>
       </c>
       <c r="B81" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82">
-        <v>127499607</v>
+        <v>127499668</v>
       </c>
       <c r="B82" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83">
-        <v>127499668</v>
+        <v>127499878</v>
       </c>
       <c r="B83" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84">
-        <v>127499878</v>
+        <v>127499971</v>
       </c>
       <c r="B84" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85">
-        <v>127499971</v>
+        <v>127500041</v>
       </c>
       <c r="B85" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86">
-        <v>127500041</v>
+        <v>127500042</v>
       </c>
       <c r="B86" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87">
-        <v>127500042</v>
+        <v>127500094</v>
       </c>
       <c r="B87" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88">
-        <v>127500094</v>
+        <v>127500119</v>
       </c>
       <c r="B88" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89">
-        <v>127500119</v>
+        <v>127500382</v>
       </c>
       <c r="B89" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90">
-        <v>127500382</v>
+        <v>127500501</v>
       </c>
       <c r="B90" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91">
-        <v>127500501</v>
+        <v>127500513</v>
       </c>
       <c r="B91" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92">
-        <v>127500513</v>
+        <v>127501000</v>
       </c>
       <c r="B92" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93">
-        <v>127501000</v>
+        <v>127501461</v>
       </c>
       <c r="B93" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94">
-        <v>127501461</v>
+        <v>127501466</v>
       </c>
       <c r="B94" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95">
-        <v>127501466</v>
+        <v>127501480</v>
       </c>
       <c r="B95" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96">
-        <v>127501480</v>
+        <v>127501500</v>
       </c>
       <c r="B96" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97">
-        <v>127501500</v>
+        <v>127501510</v>
       </c>
       <c r="B97" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98">
-        <v>127501510</v>
+        <v>127501550</v>
       </c>
       <c r="B98" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99">
-        <v>127501550</v>
+        <v>127501627</v>
       </c>
       <c r="B99" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100">
-        <v>127501627</v>
+        <v>127501641</v>
       </c>
       <c r="B100" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101">
-        <v>127501641</v>
+        <v>127501645</v>
       </c>
       <c r="B101" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102">
-        <v>127501645</v>
+        <v>127501880</v>
       </c>
       <c r="B102" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103">
-        <v>127501880</v>
+        <v>127501892</v>
       </c>
       <c r="B103" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104">
-        <v>127501892</v>
+        <v>127501963</v>
       </c>
       <c r="B104" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105">
-        <v>127501963</v>
+        <v>127502093</v>
       </c>
       <c r="B105" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106">
-        <v>127502093</v>
+        <v>127502133</v>
       </c>
       <c r="B106" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107">
-        <v>127502133</v>
+        <v>127502147</v>
       </c>
       <c r="B107" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108">
-        <v>127502147</v>
+        <v>127502253</v>
       </c>
       <c r="B108" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109">
-        <v>127502253</v>
+        <v>127502331</v>
       </c>
       <c r="B109" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110">
-        <v>127502331</v>
+        <v>127502352</v>
       </c>
       <c r="B110" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111">
-        <v>127502352</v>
+        <v>127502383</v>
       </c>
       <c r="B111" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112">
-        <v>127502383</v>
+        <v>127502425</v>
       </c>
       <c r="B112" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113">
-        <v>127502425</v>
+        <v>127502585</v>
       </c>
       <c r="B113" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114">
-        <v>127502585</v>
+        <v>127502766</v>
       </c>
       <c r="B114" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115">
-        <v>127502766</v>
+        <v>127502853</v>
       </c>
       <c r="B115" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116">
-        <v>127502853</v>
+        <v>127502859</v>
       </c>
       <c r="B116" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117">
-        <v>127502859</v>
+        <v>127503048</v>
       </c>
       <c r="B117" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118">
-        <v>127503048</v>
+        <v>127503425</v>
       </c>
       <c r="B118" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119">
-        <v>127503425</v>
+        <v>127503663</v>
       </c>
       <c r="B119" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120">
-        <v>127503663</v>
+        <v>127503781</v>
       </c>
       <c r="B120" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121">
-        <v>127503781</v>
+        <v>127503819</v>
       </c>
       <c r="B121" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122">
-        <v>127503819</v>
+        <v>127503940</v>
       </c>
       <c r="B122" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123">
-        <v>127503940</v>
+        <v>127503984</v>
       </c>
       <c r="B123" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124">
-        <v>127503984</v>
+        <v>127504062</v>
       </c>
       <c r="B124" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125">
-        <v>127504062</v>
+        <v>127504115</v>
       </c>
       <c r="B125" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126">
-        <v>127504115</v>
+        <v>127504281</v>
       </c>
       <c r="B126" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127">
-        <v>127504281</v>
+        <v>127504301</v>
       </c>
       <c r="B127" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128">
-        <v>127504301</v>
+        <v>127504305</v>
       </c>
       <c r="B128" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129">
-        <v>127504305</v>
+        <v>127504421</v>
       </c>
       <c r="B129" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130">
-        <v>127504421</v>
+        <v>127504604</v>
       </c>
       <c r="B130" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131">
-        <v>127504604</v>
+        <v>127504731</v>
       </c>
       <c r="B131" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132">
-        <v>127504731</v>
+        <v>127504770</v>
       </c>
       <c r="B132" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133">
-        <v>127504770</v>
+        <v>127504803</v>
       </c>
       <c r="B133" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134">
-        <v>127504803</v>
+        <v>127504939</v>
       </c>
       <c r="B134" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135">
-        <v>127504939</v>
+        <v>127504959</v>
       </c>
       <c r="B135" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136">
-        <v>127504959</v>
+        <v>127505029</v>
       </c>
       <c r="B136" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137">
-        <v>127505029</v>
+        <v>127505143</v>
       </c>
       <c r="B137" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138">
-        <v>127505143</v>
+        <v>127505245</v>
       </c>
       <c r="B138" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139">
-        <v>127505245</v>
+        <v>127505321</v>
       </c>
       <c r="B139" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140">
-        <v>127505321</v>
+        <v>127505378</v>
       </c>
       <c r="B140" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141">
-        <v>127505378</v>
+        <v>127505494</v>
       </c>
       <c r="B141" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142">
-        <v>127505494</v>
+        <v>127505553</v>
       </c>
       <c r="B142" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143">
-        <v>127505553</v>
+        <v>127505566</v>
       </c>
       <c r="B143" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144">
-        <v>127505566</v>
+        <v>127505576</v>
       </c>
       <c r="B144" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A145">
-        <v>127505576</v>
+        <v>127505611</v>
       </c>
       <c r="B145" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A146">
-        <v>127505611</v>
+        <v>127505681</v>
       </c>
       <c r="B146" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A147">
-        <v>127505681</v>
+        <v>127505695</v>
       </c>
       <c r="B147" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A148">
-        <v>127505695</v>
+        <v>127505704</v>
       </c>
       <c r="B148" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A149">
-        <v>127505704</v>
+        <v>127505873</v>
       </c>
       <c r="B149" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A150">
-        <v>127505873</v>
+        <v>127505895</v>
       </c>
       <c r="B150" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A151">
-        <v>127505895</v>
+        <v>127505910</v>
       </c>
       <c r="B151" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A152">
-        <v>127505910</v>
+        <v>127505991</v>
       </c>
       <c r="B152" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A153">
-        <v>127505991</v>
+        <v>127506001</v>
       </c>
       <c r="B153" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A154">
-        <v>127506001</v>
+        <v>127506077</v>
       </c>
       <c r="B154" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A155">
-        <v>127506077</v>
+        <v>127506132</v>
       </c>
       <c r="B155" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A156">
-        <v>127506132</v>
+        <v>127506180</v>
       </c>
       <c r="B156" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A157">
-        <v>127506180</v>
+        <v>127506317</v>
       </c>
       <c r="B157" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A158">
-        <v>127506317</v>
+        <v>127506321</v>
       </c>
       <c r="B158" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A159">
-        <v>127506321</v>
+        <v>127506344</v>
       </c>
       <c r="B159" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A160">
-        <v>127506344</v>
+        <v>127506371</v>
       </c>
       <c r="B160" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A161">
-        <v>127506371</v>
+        <v>127506375</v>
       </c>
       <c r="B161" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A162">
-        <v>127506375</v>
+        <v>127506432</v>
       </c>
       <c r="B162" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A163">
-        <v>127506432</v>
+        <v>127506458</v>
       </c>
       <c r="B163" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A164">
-        <v>127506458</v>
+        <v>127506470</v>
       </c>
       <c r="B164" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A165">
-        <v>127506470</v>
+        <v>127506482</v>
       </c>
       <c r="B165" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A166">
-        <v>127506482</v>
+        <v>127506515</v>
       </c>
       <c r="B166" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A167">
-        <v>127506515</v>
+        <v>127506573</v>
       </c>
       <c r="B167" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A168">
-        <v>127506573</v>
+        <v>127506659</v>
       </c>
       <c r="B168" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A169">
-        <v>127506659</v>
+        <v>127506666</v>
       </c>
       <c r="B169" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A170">
-        <v>127506666</v>
+        <v>127506668</v>
       </c>
       <c r="B170" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A171">
-        <v>127506668</v>
+        <v>127506686</v>
       </c>
       <c r="B171" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A172">
-        <v>127506686</v>
+        <v>127506727</v>
       </c>
       <c r="B172" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A173">
-        <v>127506727</v>
+        <v>127506733</v>
       </c>
       <c r="B173" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A174">
-        <v>127506733</v>
+        <v>127506738</v>
       </c>
       <c r="B174" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A175">
-        <v>127506738</v>
+        <v>127506799</v>
       </c>
       <c r="B175" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A176">
-        <v>127506799</v>
+        <v>127506858</v>
       </c>
       <c r="B176" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A177">
-        <v>127506858</v>
+        <v>127506964</v>
       </c>
       <c r="B177" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A178">
-        <v>127506964</v>
+        <v>127506972</v>
       </c>
       <c r="B178" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A179">
-        <v>127506972</v>
+        <v>127507260</v>
       </c>
       <c r="B179" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A180">
-        <v>127507260</v>
+        <v>127507296</v>
       </c>
       <c r="B180" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A181">
-        <v>127507296</v>
+        <v>127507377</v>
       </c>
       <c r="B181" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A182">
-        <v>127507377</v>
+        <v>127507452</v>
       </c>
       <c r="B182" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A183">
-        <v>127507452</v>
+        <v>127507710</v>
       </c>
       <c r="B183" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A184">
-        <v>127507710</v>
+        <v>127507717</v>
       </c>
       <c r="B184" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A185">
-        <v>127507717</v>
+        <v>127507765</v>
       </c>
       <c r="B185" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A186">
-        <v>127507765</v>
+        <v>127507932</v>
       </c>
       <c r="B186" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A187">
-        <v>127507932</v>
+        <v>127507952</v>
       </c>
       <c r="B187" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A188">
-        <v>127507952</v>
+        <v>127508077</v>
       </c>
       <c r="B188" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A189">
-        <v>127508077</v>
+        <v>127508197</v>
       </c>
       <c r="B189" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A190">
-        <v>127508197</v>
+        <v>127508324</v>
       </c>
       <c r="B190" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A191">
-        <v>127508324</v>
+        <v>127508410</v>
       </c>
       <c r="B191" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A192">
-        <v>127508410</v>
+        <v>127508429</v>
       </c>
       <c r="B192" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A193">
-        <v>127508429</v>
+        <v>127508444</v>
       </c>
       <c r="B193" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A194">
-        <v>127508444</v>
+        <v>127508491</v>
       </c>
       <c r="B194" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A195">
-        <v>127508491</v>
+        <v>127508582</v>
       </c>
       <c r="B195" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A196">
-        <v>127508582</v>
+        <v>127508593</v>
       </c>
       <c r="B196" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A197">
-        <v>127508593</v>
+        <v>127508653</v>
       </c>
       <c r="B197" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A198">
-        <v>127508653</v>
+        <v>127508684</v>
       </c>
       <c r="B198" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A199">
-        <v>127508684</v>
+        <v>127508723</v>
       </c>
       <c r="B199" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A200">
-        <v>127508723</v>
+        <v>127508801</v>
       </c>
       <c r="B200" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A201">
-        <v>127508801</v>
+        <v>127508834</v>
       </c>
       <c r="B201" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A202">
-        <v>127508834</v>
+        <v>127508843</v>
       </c>
       <c r="B202" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A203">
-        <v>127508843</v>
+        <v>127508856</v>
       </c>
       <c r="B203" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A204">
-        <v>127508856</v>
+        <v>127508914</v>
       </c>
       <c r="B204" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A205">
-        <v>127508914</v>
+        <v>127508915</v>
       </c>
       <c r="B205" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A206">
-        <v>127508915</v>
+        <v>127508920</v>
       </c>
       <c r="B206" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A207">
-        <v>127508920</v>
+        <v>127508931</v>
       </c>
       <c r="B207" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A208">
-        <v>127508931</v>
+        <v>127508991</v>
       </c>
       <c r="B208" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A209">
-        <v>127508991</v>
+        <v>127509001</v>
       </c>
       <c r="B209" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A210">
-        <v>127509001</v>
+        <v>127509023</v>
       </c>
       <c r="B210" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A211">
-        <v>127509023</v>
+        <v>127509094</v>
       </c>
       <c r="B211" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A212">
-        <v>127509094</v>
+        <v>127509131</v>
       </c>
       <c r="B212" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A213">
-        <v>127509131</v>
+        <v>127509151</v>
       </c>
       <c r="B213" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A214">
-        <v>127509151</v>
+        <v>127509187</v>
       </c>
       <c r="B214" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A215">
-        <v>127509187</v>
+        <v>127509256</v>
       </c>
       <c r="B215" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A216">
-        <v>127509256</v>
+        <v>127509288</v>
       </c>
       <c r="B216" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A217">
-        <v>127509288</v>
+        <v>127509306</v>
       </c>
       <c r="B217" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A218">
-        <v>127509306</v>
+        <v>127509342</v>
       </c>
       <c r="B218" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A219">
-        <v>127509342</v>
+        <v>127509400</v>
       </c>
       <c r="B219" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A220">
-        <v>127509400</v>
+        <v>127509464</v>
       </c>
       <c r="B220" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A221">
-        <v>127509464</v>
+        <v>127509514</v>
       </c>
       <c r="B221" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A222">
-        <v>127509514</v>
+        <v>127509533</v>
       </c>
       <c r="B222" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A223">
-        <v>127509533</v>
+        <v>127509546</v>
       </c>
       <c r="B223" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A224">
-        <v>127509546</v>
+        <v>127509567</v>
       </c>
       <c r="B224" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A225">
-        <v>127509567</v>
+        <v>127509608</v>
       </c>
       <c r="B225" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A226">
-        <v>127509608</v>
+        <v>127509636</v>
       </c>
       <c r="B226" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A227">
-        <v>127509636</v>
+        <v>127509639</v>
       </c>
       <c r="B227" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A228">
-        <v>127509639</v>
+        <v>127509756</v>
       </c>
       <c r="B228" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A229">
-        <v>127509756</v>
+        <v>127509773</v>
       </c>
       <c r="B229" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A230">
-        <v>127509773</v>
+        <v>127510078</v>
       </c>
       <c r="B230" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A231">
-        <v>127510078</v>
+        <v>127510131</v>
       </c>
       <c r="B231" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A232">
-        <v>127510131</v>
+        <v>127510210</v>
       </c>
       <c r="B232" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A233">
-        <v>127510210</v>
+        <v>127510226</v>
       </c>
       <c r="B233" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A234">
-        <v>127510226</v>
+        <v>127510270</v>
       </c>
       <c r="B234" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A235">
-        <v>127510270</v>
+        <v>127510276</v>
       </c>
       <c r="B235" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A236">
-        <v>127510276</v>
+        <v>127510434</v>
       </c>
       <c r="B236" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A237">
-        <v>127510434</v>
+        <v>127510464</v>
       </c>
       <c r="B237" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A238">
-        <v>127510464</v>
+        <v>127510528</v>
       </c>
       <c r="B238" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A239">
-        <v>127510528</v>
+        <v>127510567</v>
       </c>
       <c r="B239" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A240">
-        <v>127510567</v>
+        <v>127510612</v>
       </c>
       <c r="B240" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A241">
-        <v>127510612</v>
+        <v>127510687</v>
       </c>
       <c r="B241" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A242">
-        <v>127510687</v>
+        <v>127510711</v>
       </c>
       <c r="B242" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A243">
-        <v>127510711</v>
+        <v>127510731</v>
       </c>
       <c r="B243" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A244">
-        <v>127510731</v>
+        <v>127510807</v>
       </c>
       <c r="B244" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A245">
-        <v>127510807</v>
+        <v>127510865</v>
       </c>
       <c r="B245" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A246">
-        <v>127510865</v>
+        <v>127510867</v>
       </c>
       <c r="B246" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A247">
-        <v>127510867</v>
+        <v>127510928</v>
       </c>
       <c r="B247" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A248">
-        <v>127510928</v>
+        <v>127510967</v>
       </c>
       <c r="B248" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A249">
-        <v>127510967</v>
+        <v>127511001</v>
       </c>
       <c r="B249" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A250">
-        <v>127511001</v>
+        <v>127511048</v>
       </c>
       <c r="B250" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A251">
-        <v>127511048</v>
+        <v>127511066</v>
       </c>
       <c r="B251" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A252">
-        <v>127511066</v>
+        <v>127511087</v>
       </c>
       <c r="B252" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A253">
-        <v>127511087</v>
+        <v>127511193</v>
       </c>
       <c r="B253" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A254">
-        <v>127511193</v>
+        <v>127511587</v>
       </c>
       <c r="B254" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A255">
-        <v>127511587</v>
+        <v>127511610</v>
       </c>
       <c r="B255" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A256">
-        <v>127511610</v>
+        <v>127511655</v>
       </c>
       <c r="B256" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A257">
-        <v>127511655</v>
+        <v>127511675</v>
       </c>
       <c r="B257" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A258">
-        <v>127511675</v>
+        <v>127511718</v>
       </c>
       <c r="B258" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A259">
-        <v>127511718</v>
+        <v>127511736</v>
       </c>
       <c r="B259" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A260">
-        <v>127511736</v>
+        <v>127511740</v>
       </c>
       <c r="B260" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A261">
-        <v>127511740</v>
+        <v>127511741</v>
       </c>
       <c r="B261" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A262">
-        <v>127511741</v>
+        <v>127511744</v>
       </c>
       <c r="B262" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A263">
-        <v>127511744</v>
+        <v>127511799</v>
       </c>
       <c r="B263" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A264">
-        <v>127511799</v>
+        <v>127511843</v>
       </c>
       <c r="B264" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A265">
-        <v>127511843</v>
+        <v>127512008</v>
       </c>
       <c r="B265" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A266">
-        <v>127512008</v>
+        <v>127512093</v>
       </c>
       <c r="B266" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A267">
-        <v>127512093</v>
+        <v>127512227</v>
       </c>
       <c r="B267" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A268">
-        <v>127512227</v>
+        <v>127512252</v>
       </c>
       <c r="B268" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A269">
-        <v>127512252</v>
+        <v>127512263</v>
       </c>
       <c r="B269" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A270">
-        <v>127512263</v>
+        <v>127512323</v>
       </c>
       <c r="B270" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A271">
-        <v>127512323</v>
+        <v>127512333</v>
       </c>
       <c r="B271" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A272">
-        <v>127512333</v>
+        <v>127512359</v>
       </c>
       <c r="B272" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A273">
-        <v>127512359</v>
+        <v>127512579</v>
       </c>
       <c r="B273" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A274">
-        <v>127512579</v>
+        <v>127512611</v>
       </c>
       <c r="B274" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A275">
-        <v>127512611</v>
+        <v>127512615</v>
       </c>
       <c r="B275" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A276">
-        <v>127512615</v>
+        <v>127512653</v>
       </c>
       <c r="B276" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A277">
-        <v>127512653</v>
+        <v>127512720</v>
       </c>
       <c r="B277" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A278">
-        <v>127512720</v>
+        <v>127512789</v>
       </c>
       <c r="B278" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A279">
-        <v>127512789</v>
+        <v>127512831</v>
       </c>
       <c r="B279" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A280">
-        <v>127512831</v>
+        <v>127512864</v>
       </c>
       <c r="B280" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A281">
-        <v>127512864</v>
+        <v>127512881</v>
       </c>
       <c r="B281" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A282">
-        <v>127512881</v>
+        <v>127513062</v>
       </c>
       <c r="B282" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A283">
-        <v>127513062</v>
+        <v>127513150</v>
       </c>
       <c r="B283" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A284">
-        <v>127513150</v>
+        <v>127513191</v>
       </c>
       <c r="B284" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A285">
-        <v>127513191</v>
+        <v>127513431</v>
       </c>
       <c r="B285" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A286">
-        <v>127513431</v>
+        <v>127513436</v>
       </c>
       <c r="B286" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A287">
-        <v>127513436</v>
+        <v>127513464</v>
       </c>
       <c r="B287" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A288">
-        <v>127513464</v>
+        <v>127513680</v>
       </c>
       <c r="B288" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A289">
-        <v>127513680</v>
+        <v>127513765</v>
       </c>
       <c r="B289" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A290">
-        <v>127513765</v>
+        <v>127513797</v>
       </c>
       <c r="B290" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A291">
-        <v>127513797</v>
+        <v>127513798</v>
       </c>
       <c r="B291" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A292">
-        <v>127513798</v>
+        <v>127513827</v>
       </c>
       <c r="B292" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A293">
-        <v>127513827</v>
+        <v>127513862</v>
       </c>
       <c r="B293" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A294">
-        <v>127513862</v>
+        <v>127513942</v>
       </c>
       <c r="B294" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A295">
-        <v>127513942</v>
+        <v>127513984</v>
       </c>
       <c r="B295" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A296">
-        <v>127513984</v>
+        <v>127514012</v>
       </c>
       <c r="B296" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A297">
-        <v>127514012</v>
+        <v>127514034</v>
       </c>
       <c r="B297" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A298">
-        <v>127514034</v>
+        <v>127514063</v>
       </c>
       <c r="B298" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A299">
-        <v>127514063</v>
+        <v>127514109</v>
       </c>
       <c r="B299" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A300">
-        <v>127514109</v>
+        <v>127514163</v>
       </c>
       <c r="B300" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A301">
-        <v>127514163</v>
+        <v>127514239</v>
       </c>
       <c r="B301" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A302">
-        <v>127514239</v>
+        <v>127514268</v>
       </c>
       <c r="B302" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A303">
-        <v>127514268</v>
+        <v>127514347</v>
       </c>
       <c r="B303" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A304">
-        <v>127514347</v>
+        <v>127514413</v>
       </c>
       <c r="B304" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A305">
-        <v>127514413</v>
+        <v>127514474</v>
       </c>
       <c r="B305" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A306">
-        <v>127514474</v>
+        <v>127514545</v>
       </c>
       <c r="B306" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A307">
-        <v>127514545</v>
+        <v>127514638</v>
       </c>
       <c r="B307" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A308">
-        <v>127514638</v>
+        <v>127514753</v>
       </c>
       <c r="B308" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A309">
-        <v>127514753</v>
+        <v>127514826</v>
       </c>
       <c r="B309" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A310">
-        <v>127514826</v>
+        <v>127515004</v>
       </c>
       <c r="B310" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A311">
-        <v>127515004</v>
+        <v>127515123</v>
       </c>
       <c r="B311" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A312">
-        <v>127515123</v>
+        <v>127515183</v>
       </c>
       <c r="B312" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A313">
-        <v>127515183</v>
+        <v>127515190</v>
       </c>
       <c r="B313" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A314">
-        <v>127515190</v>
+        <v>127515364</v>
       </c>
       <c r="B314" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A315">
-        <v>127515364</v>
-      </c>
-      <c r="B315" t="s">
         <v>2</v>
       </c>
     </row>
